--- a/excel-files/QUEZON CITY/TANDANG SORA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/TANDANG SORA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29704"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="349" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84388103-FD6E-4458-9574-5F3CC0F371FE}"/>
+  <xr:revisionPtr revIDLastSave="355" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E97145-B50C-42E9-8E84-1BEEA8DCB5FE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -5470,12 +5470,15 @@
     <protectedRange sqref="F1:F98" name="SOURCE"/>
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E19" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E18 E8:E12 E2:E6" xr:uid="{633E1B5E-D854-42A9-A4E6-35C5D67258C5}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5487,7 +5490,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
-  <dimension ref="A1:AA157"/>
+  <dimension ref="A1:AA127"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -13685,186 +13688,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:27">
-      <c r="J128" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="129" spans="10:10">
-      <c r="J129" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="130" spans="10:10">
-      <c r="J130" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="131" spans="10:10">
-      <c r="J131" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="132" spans="10:10">
-      <c r="J132" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="133" spans="10:10">
-      <c r="J133" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="134" spans="10:10">
-      <c r="J134" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="135" spans="10:10">
-      <c r="J135" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="136" spans="10:10">
-      <c r="J136" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="137" spans="10:10">
-      <c r="J137" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="138" spans="10:10">
-      <c r="J138" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="139" spans="10:10">
-      <c r="J139" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="140" spans="10:10">
-      <c r="J140" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="141" spans="10:10">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="10:10">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="10:10">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="10:10">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C3 C14:C21 C23:C31 C33:C41 C43:C51 C53:C61 C63:C71 C73:C81 C83:C91 C93:C101 C103:C110 C112:C127 C5:C12" name="Textbooks"/>
@@ -13882,11 +13705,11 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F14:F21 F23:F31 F33:F41 F63:F71 F73:F81 F43:F51 X112:X127 F83:F91 F93:F101 F5:F12 F103:F110 R103:R110 L103:L110 X103:X110 F53:F61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
-    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F61 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R128 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{7B307A63-5E92-4545-8055-92E953C2B8D4}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22473,8 +22296,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 M115:M122 G3:G10 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 G12:G19" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F103:F113 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F55:F65" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L115:L122 L103:L113 L91:L101 L79:L89 L67:L77 L55:L65 L43:L53 L31:L41 L21:L29 L12:L19 L3:L10 R115:R122 R103:R113 R91:R101 R79:R89 R67:R77 R55:R65 R43:R53 R31:R41 R21:R29 R12:R19 R3:R10 X115:X122 X103:X113 X91:X101 X79:X89 X67:X77 X55:X65 X43:X53 X31:X41 X21:X29 X12:X19 X3:X10" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/excel-files/QUEZON CITY/TANDANG SORA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/QUEZON CITY/TANDANG SORA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29922"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10403"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="355" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F1E97145-B50C-42E9-8E84-1BEEA8DCB5FE}"/>
+  <xr:revisionPtr revIDLastSave="428" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25D7F9FF-B6B9-6F46-957D-92F706062600}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="93">
   <si>
     <t>Grade Level</t>
   </si>
@@ -323,7 +323,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1835,13 +1835,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -1865,6 +1858,13 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2943,13 +2943,6 @@
       </border>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color rgb="FF000000"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -2986,6 +2979,13 @@
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FF000000"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -3028,7 +3028,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="60" tableBorderDxfId="61">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}" name="Table2" displayName="Table2" ref="A1:H145" totalsRowShown="0" headerRowDxfId="62" headerRowBorderDxfId="61" tableBorderDxfId="60">
   <autoFilter ref="A1:H145" xr:uid="{DC451CB5-2E69-4EAA-94B0-458F89F93F29}"/>
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{6C961029-0F4E-47F8-B820-C81BD075C863}" name="Grade Level"/>
@@ -3045,7 +3045,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="59" headerRowBorderDxfId="57" tableBorderDxfId="58">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}" name="Table1" displayName="Table1" ref="A2:AA127" totalsRowShown="0" dataDxfId="58" headerRowBorderDxfId="59" tableBorderDxfId="57">
   <autoFilter ref="A2:AA127" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{451CCD6B-9C4E-44A3-945A-DE807169F46B}" name="Grade Level" dataDxfId="56"/>
@@ -3101,7 +3101,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="29" headerRowBorderDxfId="27" tableBorderDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{9E6A4DE0-FDA1-4B9F-927F-226E420BA323}" name="Table14" displayName="Table14" ref="A2:AA140" totalsRowShown="0" dataDxfId="28" headerRowBorderDxfId="29" tableBorderDxfId="27">
   <autoFilter ref="A2:AA140" xr:uid="{D7C37D80-F2E1-4395-8B6C-0FD477B4D8F8}"/>
   <tableColumns count="27">
     <tableColumn id="1" xr3:uid="{4B1B9E16-DDB6-464C-9C72-937B3CB9CE66}" name="Grade Level" dataDxfId="26"/>
@@ -3476,19 +3476,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H98"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.140625" customWidth="1"/>
+    <col min="1" max="1" width="10.0859375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="5" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.1015625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.19921875" customWidth="1"/>
     <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.42578125" customWidth="1"/>
-    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="9" max="9" width="16.41015625" customWidth="1"/>
+    <col min="10" max="10" width="12.10546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1">
+    <row r="1" spans="1:8" s="14" customFormat="1" ht="64.900000000000006" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="42.75" customHeight="1">
+    <row r="2" spans="1:8" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -3522,13 +3522,13 @@
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="D2" s="1">
         <v>617</v>
       </c>
       <c r="E2" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>9</v>
@@ -3539,10 +3539,10 @@
       </c>
       <c r="H2" s="4">
         <f>IF((D2-C2)&lt;0,0,D2-C2)</f>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="29.25" customHeight="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3550,16 +3550,16 @@
         <v>10</v>
       </c>
       <c r="C3" s="1">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="D3" s="1">
         <v>617</v>
       </c>
       <c r="E3" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" s="3">
         <f>IF((C3-D3)&lt;0,0,C3-D3)</f>
@@ -3567,10 +3567,10 @@
       </c>
       <c r="H3" s="4">
         <f>IF((D3-C3)&lt;0,0,D3-C3)</f>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>12</v>
       </c>
       <c r="C4" s="1">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="D4" s="1">
         <v>617</v>
@@ -3595,10 +3595,10 @@
       </c>
       <c r="H4" s="4">
         <f>IF((D4-C4)&lt;0,0,D4-C4)</f>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="25.5" customHeight="1">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3606,13 +3606,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="1">
-        <v>446</v>
+        <v>408</v>
       </c>
       <c r="D5" s="1">
         <v>617</v>
       </c>
       <c r="E5" s="1">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>9</v>
@@ -3623,10 +3623,10 @@
       </c>
       <c r="H5" s="4">
         <f t="shared" ref="H5:H6" si="1">IF((D5-C5)&lt;0,0,D5-C5)</f>
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3646,237 +3646,259 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C7" s="6"/>
       <c r="D7" s="6"/>
       <c r="E7" s="6"/>
     </row>
-    <row r="8" spans="1:8" ht="39.75" customHeight="1">
+    <row r="8" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>2</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1"/>
+      <c r="C8" s="1">
+        <v>491</v>
+      </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
       <c r="F8" s="5"/>
       <c r="G8" s="3">
         <f>IF((C8-D8)&lt;0,0,C8-D8)</f>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="H8" s="4">
         <f>IF((D8-C8)&lt;0,0,D8-C8)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="29.25" customHeight="1">
+    <row r="9" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1"/>
+      <c r="C9" s="1">
+        <v>491</v>
+      </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
       <c r="F9" s="5"/>
       <c r="G9" s="3">
         <f>IF((C9-D9)&lt;0,0,C9-D9)</f>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="H9" s="4">
         <f>IF((D9-C9)&lt;0,0,D9-C9)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="28.5" customHeight="1">
+    <row r="10" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>2</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="1"/>
+      <c r="C10" s="1">
+        <v>491</v>
+      </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
       <c r="F10" s="5"/>
       <c r="G10" s="3">
         <f>IF((C10-D10)&lt;0,0,C10-D10)</f>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="H10" s="4">
         <f>IF((D10-C10)&lt;0,0,D10-C10)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="24" customHeight="1">
+    <row r="11" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>2</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="1"/>
+      <c r="C11" s="1">
+        <v>491</v>
+      </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
       <c r="F11" s="5"/>
       <c r="G11" s="3">
         <f>IF((C11-D11)&lt;0,0,C11-D11)</f>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="H11" s="4">
         <f>IF((D11-C11)&lt;0,0,D11-C11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="19.149999999999999">
+    <row r="12" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="1"/>
+      <c r="C12" s="1">
+        <v>491</v>
+      </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="5"/>
       <c r="G12" s="3">
         <f>IF((C12-D12)&lt;0,0,C12-D12)</f>
-        <v>0</v>
+        <v>491</v>
       </c>
       <c r="H12" s="4">
         <f>IF((D12-C12)&lt;0,0,D12-C12)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="C13" s="6"/>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
     </row>
-    <row r="14" spans="1:8" ht="49.5" customHeight="1">
+    <row r="14" spans="1:8" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>3</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="1"/>
+      <c r="C14" s="1">
+        <v>478</v>
+      </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="5"/>
       <c r="G14" s="3">
         <f t="shared" ref="G14:G19" si="2">IF((C14-D14)&lt;0,0,C14-D14)</f>
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="H14" s="4">
         <f t="shared" ref="H14:H19" si="3">IF((D14-C14)&lt;0,0,D14-C14)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="29.25" customHeight="1">
+    <row r="15" spans="1:8" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="1"/>
+      <c r="C15" s="1">
+        <v>478</v>
+      </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="5"/>
       <c r="G15" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="H15" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="27" customHeight="1">
+    <row r="16" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>3</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="1"/>
+      <c r="C16" s="1">
+        <v>478</v>
+      </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
       <c r="F16" s="5"/>
       <c r="G16" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="H16" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="23.25" customHeight="1">
+    <row r="17" spans="1:8" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>3</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="1"/>
+      <c r="C17" s="1">
+        <v>478</v>
+      </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
       <c r="F17" s="5"/>
       <c r="G17" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="H17" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="21" customHeight="1">
+    <row r="18" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>3</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C18" s="1"/>
+      <c r="C18" s="1">
+        <v>478</v>
+      </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
       <c r="F18" s="5"/>
       <c r="G18" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="H18" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="19.149999999999999">
+    <row r="19" spans="1:8" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>3</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="1"/>
+      <c r="C19" s="1">
+        <v>478</v>
+      </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
       <c r="F19" s="5"/>
       <c r="G19" s="3">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>478</v>
       </c>
       <c r="H19" s="4">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="8"/>
@@ -3886,7 +3908,7 @@
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" ht="28.5" customHeight="1">
+    <row r="21" spans="1:8" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>4</v>
       </c>
@@ -3894,27 +3916,21 @@
         <v>16</v>
       </c>
       <c r="C21" s="1">
-        <v>620</v>
-      </c>
-      <c r="D21" s="1">
         <v>539</v>
       </c>
-      <c r="E21" s="1">
-        <v>2024</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>17</v>
-      </c>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="5"/>
       <c r="G21" s="3">
         <f t="shared" ref="G21:G29" si="4">IF((C21-D21)&lt;0,0,C21-D21)</f>
-        <v>81</v>
+        <v>539</v>
       </c>
       <c r="H21" s="4">
         <f t="shared" ref="H21:H29" si="5">IF((D21-C21)&lt;0,0,D21-C21)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="24" customHeight="1">
+    <row r="22" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -3922,10 +3938,10 @@
         <v>18</v>
       </c>
       <c r="C22" s="1">
+        <v>539</v>
+      </c>
+      <c r="D22" s="1">
         <v>620</v>
-      </c>
-      <c r="D22" s="1">
-        <v>539</v>
       </c>
       <c r="E22" s="1">
         <v>2024</v>
@@ -3935,14 +3951,14 @@
       </c>
       <c r="G22" s="3">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H22" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="19.5">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="18" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -3950,27 +3966,27 @@
         <v>14</v>
       </c>
       <c r="C23" s="1">
+        <v>539</v>
+      </c>
+      <c r="D23" s="1">
         <v>620</v>
       </c>
-      <c r="D23" s="1">
-        <v>539</v>
-      </c>
       <c r="E23" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F23" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="3">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H23" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="27" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -3978,27 +3994,27 @@
         <v>12</v>
       </c>
       <c r="C24" s="1">
+        <v>539</v>
+      </c>
+      <c r="D24" s="1">
         <v>620</v>
       </c>
-      <c r="D24" s="1">
-        <v>539</v>
-      </c>
       <c r="E24" s="1">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="F24" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="3">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H24" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="33.75" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4006,10 +4022,10 @@
         <v>19</v>
       </c>
       <c r="C25" s="1">
+        <v>539</v>
+      </c>
+      <c r="D25" s="1">
         <v>620</v>
-      </c>
-      <c r="D25" s="1">
-        <v>539</v>
       </c>
       <c r="E25" s="1">
         <v>2024</v>
@@ -4019,14 +4035,14 @@
       </c>
       <c r="G25" s="3">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H25" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="33.75" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4034,10 +4050,10 @@
         <v>15</v>
       </c>
       <c r="C26" s="1">
+        <v>539</v>
+      </c>
+      <c r="D26" s="1">
         <v>620</v>
-      </c>
-      <c r="D26" s="1">
-        <v>536</v>
       </c>
       <c r="E26" s="1">
         <v>2024</v>
@@ -4047,14 +4063,14 @@
       </c>
       <c r="G26" s="3">
         <f t="shared" si="4"/>
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="H26" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="33.75" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4062,10 +4078,10 @@
         <v>20</v>
       </c>
       <c r="C27" s="1">
+        <v>539</v>
+      </c>
+      <c r="D27" s="1">
         <v>620</v>
-      </c>
-      <c r="D27" s="1">
-        <v>539</v>
       </c>
       <c r="E27" s="1">
         <v>2024</v>
@@ -4075,54 +4091,64 @@
       </c>
       <c r="G27" s="3">
         <f t="shared" si="4"/>
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="H27" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="27.75" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>4</v>
       </c>
       <c r="B28" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="1"/>
+      <c r="C28" s="1">
+        <v>539</v>
+      </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="3">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>539</v>
       </c>
       <c r="H28" s="4">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>4</v>
       </c>
       <c r="B29" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="C29" s="1">
+        <v>539</v>
+      </c>
+      <c r="D29" s="1">
+        <v>620</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27.75" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="7"/>
       <c r="B30" s="7"/>
       <c r="C30" s="8"/>
@@ -4132,7 +4158,7 @@
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -4140,87 +4166,93 @@
         <v>16</v>
       </c>
       <c r="C31" s="1">
+        <v>463</v>
+      </c>
+      <c r="D31" s="1">
         <v>550</v>
-      </c>
-      <c r="D31" s="1">
-        <v>461</v>
       </c>
       <c r="E31" s="1">
         <v>2025</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G31" s="3">
         <f t="shared" ref="G31:G39" si="6">IF((C31-D31)&lt;0,0,C31-D31)</f>
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H31" s="4">
         <f t="shared" ref="H31:H39" si="7">IF((D31-C31)&lt;0,0,D31-C31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" ht="27.75" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>5</v>
       </c>
       <c r="B32" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C32" s="1"/>
+      <c r="C32" s="1">
+        <v>463</v>
+      </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
       <c r="F32" s="5"/>
       <c r="G32" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>5</v>
       </c>
       <c r="B33" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C33" s="1"/>
+      <c r="C33" s="1">
+        <v>463</v>
+      </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
       <c r="F33" s="5"/>
       <c r="G33" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="H33" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>5</v>
       </c>
       <c r="B34" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="1"/>
+      <c r="C34" s="1">
+        <v>463</v>
+      </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="5"/>
       <c r="G34" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="H34" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="39" customHeight="1">
+    <row r="35" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4228,27 +4260,27 @@
         <v>19</v>
       </c>
       <c r="C35" s="1">
+        <v>463</v>
+      </c>
+      <c r="D35" s="1">
         <v>550</v>
-      </c>
-      <c r="D35" s="1">
-        <v>461</v>
       </c>
       <c r="E35" s="1">
         <v>2025</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G35" s="3">
         <f t="shared" si="6"/>
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H35" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="27.75" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4256,27 +4288,27 @@
         <v>15</v>
       </c>
       <c r="C36" s="1">
+        <v>463</v>
+      </c>
+      <c r="D36" s="1">
         <v>550</v>
       </c>
-      <c r="D36" s="1">
-        <v>461</v>
-      </c>
       <c r="E36" s="1">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G36" s="3">
         <f t="shared" si="6"/>
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H36" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="27.75" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4284,67 +4316,77 @@
         <v>20</v>
       </c>
       <c r="C37" s="1">
+        <v>463</v>
+      </c>
+      <c r="D37" s="1">
         <v>550</v>
-      </c>
-      <c r="D37" s="1">
-        <v>461</v>
       </c>
       <c r="E37" s="1">
         <v>2025</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G37" s="3">
         <f t="shared" si="6"/>
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H37" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" ht="27.75" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>5</v>
       </c>
       <c r="B38" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="5"/>
+      <c r="C38" s="1">
+        <v>463</v>
+      </c>
+      <c r="D38" s="1">
+        <v>550</v>
+      </c>
+      <c r="E38" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>17</v>
+      </c>
       <c r="G38" s="3">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H38" s="4">
         <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" ht="27.75" customHeight="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>5</v>
       </c>
       <c r="B39" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C39" s="1"/>
+      <c r="C39" s="1">
+        <v>463</v>
+      </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
       <c r="F39" s="5"/>
       <c r="G39" s="3">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>463</v>
       </c>
       <c r="H39" s="4">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="7"/>
       <c r="B40" s="7"/>
       <c r="C40" s="8"/>
@@ -4354,187 +4396,205 @@
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" ht="27.75" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>6</v>
       </c>
       <c r="B41" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C41" s="1"/>
+      <c r="C41" s="1">
+        <v>445</v>
+      </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
       <c r="F41" s="5"/>
       <c r="G41" s="3">
         <f t="shared" ref="G41:G49" si="8">IF((C41-D41)&lt;0,0,C41-D41)</f>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H41" s="4">
         <f t="shared" ref="H41:H49" si="9">IF((D41-C41)&lt;0,0,D41-C41)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:8" ht="27.75" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
         <v>6</v>
       </c>
       <c r="B42" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="C42" s="1"/>
+      <c r="C42" s="1">
+        <v>445</v>
+      </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
       <c r="F42" s="5"/>
       <c r="G42" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H42" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>6</v>
       </c>
       <c r="B43" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="C43" s="1"/>
+      <c r="C43" s="1">
+        <v>445</v>
+      </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
       <c r="G43" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H43" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>6</v>
       </c>
       <c r="B44" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C44" s="1"/>
+      <c r="C44" s="1">
+        <v>445</v>
+      </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="5"/>
       <c r="G44" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H44" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="36.75" customHeight="1">
+    <row r="45" spans="1:8" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>6</v>
       </c>
       <c r="B45" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C45" s="1"/>
+      <c r="C45" s="1">
+        <v>445</v>
+      </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
       <c r="F45" s="5"/>
       <c r="G45" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H45" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="27.75" customHeight="1">
+    <row r="46" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>6</v>
       </c>
       <c r="B46" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C46" s="1"/>
+      <c r="C46" s="1">
+        <v>445</v>
+      </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="5"/>
       <c r="G46" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H46" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>6</v>
       </c>
       <c r="B47" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C47" s="1"/>
+      <c r="C47" s="1">
+        <v>445</v>
+      </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
       <c r="F47" s="5"/>
       <c r="G47" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H47" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>6</v>
       </c>
       <c r="B48" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="C48" s="1"/>
+      <c r="C48" s="1">
+        <v>445</v>
+      </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="5"/>
       <c r="G48" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H48" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>6</v>
       </c>
       <c r="B49" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C49" s="1"/>
+      <c r="C49" s="1">
+        <v>445</v>
+      </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
       <c r="F49" s="5"/>
       <c r="G49" s="3">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>445</v>
       </c>
       <c r="H49" s="4">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="7"/>
       <c r="B50" s="7"/>
       <c r="C50" s="8"/>
@@ -4544,7 +4604,7 @@
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" ht="27.75" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>7</v>
       </c>
@@ -4564,7 +4624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:8" ht="27.75" customHeight="1">
+    <row r="52" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>7</v>
       </c>
@@ -4584,7 +4644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:8" ht="27.75" customHeight="1">
+    <row r="53" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>7</v>
       </c>
@@ -4604,7 +4664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" ht="27.75" customHeight="1">
+    <row r="54" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>7</v>
       </c>
@@ -4624,7 +4684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:8" ht="39" customHeight="1">
+    <row r="55" spans="1:8" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>7</v>
       </c>
@@ -4644,7 +4704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:8" ht="27.75" customHeight="1">
+    <row r="56" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>7</v>
       </c>
@@ -4664,7 +4724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:8" ht="27.75" customHeight="1">
+    <row r="57" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>7</v>
       </c>
@@ -4684,7 +4744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="27.75" customHeight="1">
+    <row r="58" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>7</v>
       </c>
@@ -4704,7 +4764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="27.75" customHeight="1">
+    <row r="59" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>7</v>
       </c>
@@ -4724,7 +4784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:8" ht="27.75" customHeight="1">
+    <row r="60" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="7"/>
       <c r="B60" s="7"/>
       <c r="C60" s="8"/>
@@ -4734,7 +4794,7 @@
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
     </row>
-    <row r="61" spans="1:8" ht="27.75" customHeight="1">
+    <row r="61" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>8</v>
       </c>
@@ -4754,7 +4814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:8" ht="27.75" customHeight="1">
+    <row r="62" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>8</v>
       </c>
@@ -4774,7 +4834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:8" ht="27.75" customHeight="1">
+    <row r="63" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>8</v>
       </c>
@@ -4794,7 +4854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:8" ht="27.75" customHeight="1">
+    <row r="64" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>8</v>
       </c>
@@ -4814,7 +4874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:8" ht="27.75" customHeight="1">
+    <row r="65" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>8</v>
       </c>
@@ -4834,7 +4894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:8" ht="27.75" customHeight="1">
+    <row r="66" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>8</v>
       </c>
@@ -4854,7 +4914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:8" ht="27.75" customHeight="1">
+    <row r="67" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>8</v>
       </c>
@@ -4874,7 +4934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:8" ht="27.75" customHeight="1">
+    <row r="68" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>8</v>
       </c>
@@ -4894,7 +4954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:8" ht="27.75" customHeight="1">
+    <row r="69" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>8</v>
       </c>
@@ -4914,7 +4974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:8" ht="27.75" customHeight="1">
+    <row r="70" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="7"/>
       <c r="B70" s="7"/>
       <c r="C70" s="8"/>
@@ -4924,7 +4984,7 @@
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" ht="27.75" customHeight="1">
+    <row r="71" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>9</v>
       </c>
@@ -4944,7 +5004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:8" ht="27.75" customHeight="1">
+    <row r="72" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>9</v>
       </c>
@@ -4964,7 +5024,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:8" ht="27.75" customHeight="1">
+    <row r="73" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>9</v>
       </c>
@@ -4984,7 +5044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:8" ht="27.75" customHeight="1">
+    <row r="74" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>9</v>
       </c>
@@ -5004,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:8" ht="27.75" customHeight="1">
+    <row r="75" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>9</v>
       </c>
@@ -5024,7 +5084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:8" ht="27.75" customHeight="1">
+    <row r="76" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>9</v>
       </c>
@@ -5044,7 +5104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:8" ht="27.75" customHeight="1">
+    <row r="77" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>9</v>
       </c>
@@ -5064,7 +5124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:8" ht="27.75" customHeight="1">
+    <row r="78" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>9</v>
       </c>
@@ -5084,7 +5144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:8" ht="27.75" customHeight="1">
+    <row r="79" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>9</v>
       </c>
@@ -5104,7 +5164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:8" ht="27.75" customHeight="1">
+    <row r="80" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="7"/>
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
@@ -5114,7 +5174,7 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" ht="27.75" customHeight="1">
+    <row r="81" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>10</v>
       </c>
@@ -5134,7 +5194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:8" ht="27.75" customHeight="1">
+    <row r="82" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>10</v>
       </c>
@@ -5154,7 +5214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:8" ht="27.75" customHeight="1">
+    <row r="83" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>10</v>
       </c>
@@ -5174,7 +5234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:8" ht="27.75" customHeight="1">
+    <row r="84" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>10</v>
       </c>
@@ -5194,7 +5254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:8" ht="27.75" customHeight="1">
+    <row r="85" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>10</v>
       </c>
@@ -5214,7 +5274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:8" ht="27.75" customHeight="1">
+    <row r="86" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>10</v>
       </c>
@@ -5234,7 +5294,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:8" ht="27.75" customHeight="1">
+    <row r="87" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>10</v>
       </c>
@@ -5254,7 +5314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:8" ht="27.75" customHeight="1">
+    <row r="88" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>10</v>
       </c>
@@ -5274,7 +5334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:8" ht="27.75" customHeight="1">
+    <row r="89" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>10</v>
       </c>
@@ -5294,7 +5354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:8" ht="27.75" customHeight="1">
+    <row r="90" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="7"/>
       <c r="B90" s="7"/>
       <c r="C90" s="8"/>
@@ -5304,7 +5364,7 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" ht="39.75" customHeight="1">
+    <row r="91" spans="1:8" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>26</v>
       </c>
@@ -5324,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:8" ht="27.75" customHeight="1">
+    <row r="92" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>26</v>
       </c>
@@ -5344,7 +5404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:8" ht="27.75" customHeight="1">
+    <row r="93" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>26</v>
       </c>
@@ -5364,7 +5424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="27.75" customHeight="1">
+    <row r="94" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>26</v>
       </c>
@@ -5384,7 +5444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:8" ht="40.5" customHeight="1">
+    <row r="95" spans="1:8" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>26</v>
       </c>
@@ -5404,7 +5464,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:8" ht="38.25" customHeight="1">
+    <row r="96" spans="1:8" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>26</v>
       </c>
@@ -5424,7 +5484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:8" ht="27.75" customHeight="1">
+    <row r="97" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>26</v>
       </c>
@@ -5444,7 +5504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:8" ht="47.25" customHeight="1">
+    <row r="98" spans="1:8" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>26</v>
       </c>
@@ -5474,7 +5534,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E19" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F91:F98 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F31:F39" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E18 E8:E12 E2:E6" xr:uid="{633E1B5E-D854-42A9-A4E6-35C5D67258C5}">
@@ -5491,35 +5551,35 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0858F8C8-8AF8-4852-B88C-61047AF726C8}">
   <dimension ref="A1:AA127"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="26.140625" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="35.5703125" customWidth="1"/>
-    <col min="12" max="12" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="31.5703125" customWidth="1"/>
-    <col min="14" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="33.42578125" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="26.09765625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="35.51171875" customWidth="1"/>
+    <col min="12" max="12" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="31.609375" customWidth="1"/>
+    <col min="14" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="33.359375" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D1" s="42" t="s">
         <v>35</v>
       </c>
@@ -5553,7 +5613,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -5636,7 +5696,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="30.6" customHeight="1">
+    <row r="3" spans="1:27" ht="30.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="39" t="s">
         <v>63</v>
       </c>
@@ -5705,7 +5765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="4" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J4" s="13"/>
       <c r="N4" s="13"/>
       <c r="O4" s="13"/>
@@ -5717,7 +5777,7 @@
       <c r="Z4" s="13"/>
       <c r="AA4" s="13"/>
     </row>
-    <row r="5" spans="1:27" ht="37.5" customHeight="1">
+    <row r="5" spans="1:27" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -5790,7 +5850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -5863,7 +5923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -5936,7 +5996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6009,7 +6069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6082,7 +6142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6155,7 +6215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.5">
+    <row r="11" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6228,7 +6288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.5">
+    <row r="12" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6301,7 +6361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="13" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J13" s="13"/>
       <c r="N13" s="13"/>
       <c r="O13" s="13"/>
@@ -6314,7 +6374,7 @@
       <c r="Z13" s="13"/>
       <c r="AA13" s="13"/>
     </row>
-    <row r="14" spans="1:27" ht="36" customHeight="1">
+    <row r="14" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -6387,7 +6447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6460,7 +6520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6533,7 +6593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6606,7 +6666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -6679,7 +6739,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -6752,7 +6812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.5">
+    <row r="20" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -6825,7 +6885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.5">
+    <row r="21" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -6898,7 +6958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="22" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J22" s="13"/>
       <c r="M22" s="5"/>
       <c r="N22" s="13"/>
@@ -6912,7 +6972,7 @@
       <c r="Z22" s="13"/>
       <c r="AA22" s="13"/>
     </row>
-    <row r="23" spans="1:27" ht="30" customHeight="1">
+    <row r="23" spans="1:27" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -6985,7 +7045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7058,7 +7118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7131,7 +7191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7204,7 +7264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7277,7 +7337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7350,7 +7410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7423,7 +7483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.5">
+    <row r="30" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7496,7 +7556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7569,7 +7629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="32" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J32" s="13"/>
       <c r="M32" s="5"/>
       <c r="N32" s="13"/>
@@ -7583,7 +7643,7 @@
       <c r="Z32" s="13"/>
       <c r="AA32" s="13"/>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -7656,7 +7716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -7729,7 +7789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.5">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -7802,7 +7862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -7875,7 +7935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="36" customHeight="1">
+    <row r="37" spans="1:27" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -7948,7 +8008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8021,7 +8081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8094,7 +8154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8167,7 +8227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8240,7 +8300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="42" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J42" s="13"/>
       <c r="M42" s="5"/>
       <c r="N42" s="13"/>
@@ -8254,7 +8314,7 @@
       <c r="Z42" s="13"/>
       <c r="AA42" s="13"/>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -8327,7 +8387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8400,7 +8460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8473,7 +8533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8546,7 +8606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="34.5" customHeight="1">
+    <row r="47" spans="1:27" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8619,7 +8679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8692,7 +8752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8765,7 +8825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -8838,7 +8898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -8911,7 +8971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="52" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J52" s="13"/>
       <c r="M52" s="5"/>
       <c r="N52" s="13"/>
@@ -8925,7 +8985,7 @@
       <c r="Z52" s="13"/>
       <c r="AA52" s="13"/>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>6</v>
       </c>
@@ -8998,7 +9058,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9071,7 +9131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9144,7 +9204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9217,7 +9277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="36.75" customHeight="1">
+    <row r="57" spans="1:27" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9290,7 +9350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9363,7 +9423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.5">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9436,7 +9496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9509,7 +9569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9582,7 +9642,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="62" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J62" s="13"/>
       <c r="M62" s="5"/>
       <c r="N62" s="13"/>
@@ -9596,7 +9656,7 @@
       <c r="Z62" s="13"/>
       <c r="AA62" s="13"/>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>7</v>
       </c>
@@ -9665,7 +9725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>7</v>
       </c>
@@ -9734,7 +9794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>7</v>
       </c>
@@ -9803,7 +9863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999">
+    <row r="66" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>7</v>
       </c>
@@ -9872,7 +9932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="19.149999999999999">
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -9941,7 +10001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -10010,7 +10070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -10079,7 +10139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -10148,7 +10208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -10217,7 +10277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="72" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J72" s="13"/>
       <c r="M72" s="5"/>
       <c r="N72" s="13"/>
@@ -10231,7 +10291,7 @@
       <c r="Z72" s="13"/>
       <c r="AA72" s="13"/>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>8</v>
       </c>
@@ -10300,7 +10360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>8</v>
       </c>
@@ -10369,7 +10429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>8</v>
       </c>
@@ -10438,7 +10498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>8</v>
       </c>
@@ -10507,7 +10567,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>8</v>
       </c>
@@ -10576,7 +10636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="19.149999999999999">
+    <row r="78" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>8</v>
       </c>
@@ -10645,7 +10705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="19.149999999999999">
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -10714,7 +10774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -10783,7 +10843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -10852,7 +10912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="82" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J82" s="13"/>
       <c r="M82" s="5"/>
       <c r="N82" s="13"/>
@@ -10866,7 +10926,7 @@
       <c r="Z82" s="13"/>
       <c r="AA82" s="13"/>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>9</v>
       </c>
@@ -10935,7 +10995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>9</v>
       </c>
@@ -11004,7 +11064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>9</v>
       </c>
@@ -11073,7 +11133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>9</v>
       </c>
@@ -11142,7 +11202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>9</v>
       </c>
@@ -11211,7 +11271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>9</v>
       </c>
@@ -11280,7 +11340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>9</v>
       </c>
@@ -11349,7 +11409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" ht="19.149999999999999">
+    <row r="90" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>9</v>
       </c>
@@ -11418,7 +11478,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -11487,7 +11547,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="92" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J92" s="13"/>
       <c r="M92" s="5"/>
       <c r="N92" s="13"/>
@@ -11501,7 +11561,7 @@
       <c r="Z92" s="13"/>
       <c r="AA92" s="13"/>
     </row>
-    <row r="93" spans="1:27" ht="19.149999999999999">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>10</v>
       </c>
@@ -11570,7 +11630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.149999999999999">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>10</v>
       </c>
@@ -11639,7 +11699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.149999999999999">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>10</v>
       </c>
@@ -11708,7 +11768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.149999999999999">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>10</v>
       </c>
@@ -11777,7 +11837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.149999999999999">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>10</v>
       </c>
@@ -11846,7 +11906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.149999999999999">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>10</v>
       </c>
@@ -11915,7 +11975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.149999999999999">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>10</v>
       </c>
@@ -11984,7 +12044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.149999999999999">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>10</v>
       </c>
@@ -12053,7 +12113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.149999999999999">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>10</v>
       </c>
@@ -12122,7 +12182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="102" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J102" s="13"/>
       <c r="M102" s="5"/>
       <c r="N102" s="13"/>
@@ -12136,7 +12196,7 @@
       <c r="Z102" s="13"/>
       <c r="AA102" s="13"/>
     </row>
-    <row r="103" spans="1:27" ht="38.450000000000003">
+    <row r="103" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>26</v>
       </c>
@@ -12205,7 +12265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.149999999999999">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>26</v>
       </c>
@@ -12274,7 +12334,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.149999999999999">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>26</v>
       </c>
@@ -12343,7 +12403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.149999999999999">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>26</v>
       </c>
@@ -12412,7 +12472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="38.450000000000003">
+    <row r="107" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>26</v>
       </c>
@@ -12481,7 +12541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.149999999999999">
+    <row r="108" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>26</v>
       </c>
@@ -12550,7 +12610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="38.450000000000003">
+    <row r="109" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>26</v>
       </c>
@@ -12619,7 +12679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="38.450000000000003">
+    <row r="110" spans="1:27" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>26</v>
       </c>
@@ -12688,7 +12748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
+    <row r="111" spans="1:27" s="7" customFormat="1" ht="20.25" x14ac:dyDescent="0.2">
       <c r="J111" s="13"/>
       <c r="N111" s="13"/>
       <c r="O111" s="13"/>
@@ -12699,7 +12759,7 @@
       <c r="Z111" s="13"/>
       <c r="AA111" s="13"/>
     </row>
-    <row r="112" spans="1:27" ht="19.149999999999999">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="1"/>
       <c r="B112" s="9"/>
       <c r="C112" s="1"/>
@@ -12761,7 +12821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:27" ht="19.149999999999999">
+    <row r="113" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="1"/>
       <c r="B113" s="9"/>
       <c r="C113" s="1"/>
@@ -12823,7 +12883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:27" ht="19.149999999999999">
+    <row r="114" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A114" s="1"/>
       <c r="B114" s="9"/>
       <c r="C114" s="1"/>
@@ -12885,7 +12945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:27" ht="19.149999999999999">
+    <row r="115" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A115" s="1"/>
       <c r="B115" s="9"/>
       <c r="C115" s="1"/>
@@ -12947,7 +13007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:27" ht="19.149999999999999">
+    <row r="116" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1"/>
       <c r="B116" s="9"/>
       <c r="C116" s="1"/>
@@ -13009,7 +13069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:27" ht="19.149999999999999">
+    <row r="117" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1"/>
       <c r="B117" s="9"/>
       <c r="C117" s="1"/>
@@ -13071,7 +13131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:27" ht="19.149999999999999">
+    <row r="118" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1"/>
       <c r="B118" s="9"/>
       <c r="C118" s="1"/>
@@ -13133,7 +13193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:27" ht="19.149999999999999">
+    <row r="119" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A119" s="1"/>
       <c r="B119" s="9"/>
       <c r="C119" s="1"/>
@@ -13195,7 +13255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:27" ht="19.149999999999999">
+    <row r="120" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A120" s="1"/>
       <c r="B120" s="9"/>
       <c r="C120" s="1"/>
@@ -13257,7 +13317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:27" ht="19.149999999999999">
+    <row r="121" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A121" s="1"/>
       <c r="B121" s="9"/>
       <c r="C121" s="1"/>
@@ -13319,7 +13379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:27" ht="19.149999999999999">
+    <row r="122" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A122" s="1"/>
       <c r="B122" s="9"/>
       <c r="C122" s="1"/>
@@ -13381,7 +13441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:27" ht="19.149999999999999">
+    <row r="123" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A123" s="1"/>
       <c r="B123" s="9"/>
       <c r="C123" s="1"/>
@@ -13443,7 +13503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:27" ht="19.149999999999999">
+    <row r="124" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A124" s="1"/>
       <c r="B124" s="9"/>
       <c r="C124" s="1"/>
@@ -13505,7 +13565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:27" ht="19.149999999999999">
+    <row r="125" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A125" s="1"/>
       <c r="B125" s="9"/>
       <c r="C125" s="1"/>
@@ -13567,7 +13627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:27" ht="19.149999999999999">
+    <row r="126" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A126" s="1"/>
       <c r="B126" s="9"/>
       <c r="C126" s="1"/>
@@ -13629,7 +13689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:27" ht="19.149999999999999">
+    <row r="127" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A127" s="29"/>
       <c r="B127" s="30"/>
       <c r="C127" s="29"/>
@@ -13725,34 +13785,34 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
   <dimension ref="A1:AB140"/>
-  <sheetFormatPr defaultRowHeight="13.9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.85546875" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" customWidth="1"/>
-    <col min="5" max="5" width="23.140625" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.5703125" customWidth="1"/>
-    <col min="8" max="9" width="20.85546875" customWidth="1"/>
-    <col min="10" max="10" width="13.7109375" customWidth="1"/>
-    <col min="11" max="11" width="24.42578125" customWidth="1"/>
-    <col min="12" max="12" width="18.140625" customWidth="1"/>
-    <col min="13" max="15" width="20.85546875" customWidth="1"/>
-    <col min="16" max="16" width="21.5703125" customWidth="1"/>
-    <col min="17" max="17" width="29.140625" customWidth="1"/>
-    <col min="18" max="18" width="25.85546875" customWidth="1"/>
-    <col min="19" max="19" width="32.85546875" customWidth="1"/>
-    <col min="20" max="21" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.4140625" customWidth="1"/>
+    <col min="2" max="2" width="27.84375" customWidth="1"/>
+    <col min="3" max="3" width="17.08203125" customWidth="1"/>
+    <col min="4" max="4" width="16.41015625" customWidth="1"/>
+    <col min="5" max="5" width="23.13671875" customWidth="1"/>
+    <col min="6" max="6" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.5625" customWidth="1"/>
+    <col min="8" max="9" width="20.84765625" customWidth="1"/>
+    <col min="10" max="10" width="13.71875" customWidth="1"/>
+    <col min="11" max="11" width="24.48046875" customWidth="1"/>
+    <col min="12" max="12" width="18.16015625" customWidth="1"/>
+    <col min="13" max="15" width="20.84765625" customWidth="1"/>
+    <col min="16" max="16" width="21.5234375" customWidth="1"/>
+    <col min="17" max="17" width="29.19140625" customWidth="1"/>
+    <col min="18" max="18" width="25.828125" customWidth="1"/>
+    <col min="19" max="19" width="32.8203125" customWidth="1"/>
+    <col min="20" max="21" width="20.84765625" customWidth="1"/>
     <col min="22" max="22" width="16.140625" customWidth="1"/>
-    <col min="23" max="23" width="25" customWidth="1"/>
-    <col min="24" max="24" width="15.28515625" customWidth="1"/>
-    <col min="25" max="25" width="20.85546875" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" customWidth="1"/>
-    <col min="27" max="27" width="15.140625" customWidth="1"/>
+    <col min="23" max="23" width="25.01953125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
+    <col min="25" max="25" width="20.84765625" customWidth="1"/>
+    <col min="26" max="26" width="14.796875" customWidth="1"/>
+    <col min="27" max="27" width="15.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1">
+    <row r="1" spans="1:27" s="28" customFormat="1" ht="34.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B1" s="35"/>
       <c r="D1" s="42" t="s">
         <v>35</v>
@@ -13787,7 +13847,7 @@
       <c r="Z1" s="45"/>
       <c r="AA1" s="45"/>
     </row>
-    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1">
+    <row r="2" spans="1:27" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="15" t="s">
         <v>0</v>
       </c>
@@ -13870,7 +13930,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="32.25" customHeight="1">
+    <row r="3" spans="1:27" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -13945,7 +14005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="19.5">
+    <row r="4" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -14020,7 +14080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.5">
+    <row r="5" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -14096,7 +14156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.5">
+    <row r="6" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14172,7 +14232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.5">
+    <row r="7" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14248,7 +14308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.5">
+    <row r="8" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14324,7 +14384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.5">
+    <row r="9" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14400,7 +14460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.5">
+    <row r="10" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14476,13 +14536,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" s="7" customFormat="1">
+    <row r="11" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F11" s="7">
         <f>2026 - Table14[[#This Row],[Grade Level]]</f>
         <v>2026</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="33" customHeight="1">
+    <row r="12" spans="1:27" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -14558,7 +14618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.5">
+    <row r="13" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14634,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.5">
+    <row r="14" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14710,7 +14770,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.5">
+    <row r="15" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14786,7 +14846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.5">
+    <row r="16" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14862,7 +14922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.5">
+    <row r="17" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14938,7 +14998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.5">
+    <row r="18" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -15014,7 +15074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.5">
+    <row r="19" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -15090,8 +15150,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="34.5" customHeight="1">
+    <row r="20" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:27" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -15164,7 +15224,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.5">
+    <row r="22" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15237,7 +15297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.5">
+    <row r="23" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15310,7 +15370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.5">
+    <row r="24" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15383,7 +15443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.5">
+    <row r="25" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15456,7 +15516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.5">
+    <row r="26" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15529,7 +15589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.5">
+    <row r="27" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15602,7 +15662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.5">
+    <row r="28" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15675,7 +15735,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.5">
+    <row r="29" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15748,13 +15808,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" s="7" customFormat="1">
+    <row r="30" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F30" s="7">
         <f>2026 - Table14[[#This Row],[Grade Level]]</f>
         <v>2026</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.5">
+    <row r="31" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>4</v>
       </c>
@@ -15827,7 +15887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.5">
+    <row r="32" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15900,7 +15960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.5">
+    <row r="33" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15973,7 +16033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.5">
+    <row r="34" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -16046,7 +16106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="38.25">
+    <row r="35" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -16119,7 +16179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.5">
+    <row r="36" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -16192,7 +16252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.5">
+    <row r="37" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16265,7 +16325,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.5">
+    <row r="38" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16338,7 +16398,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.5">
+    <row r="39" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16411,7 +16471,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.5">
+    <row r="40" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16484,7 +16544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.5">
+    <row r="41" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16557,13 +16617,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" s="7" customFormat="1">
+    <row r="42" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F42" s="7">
         <f>2026 - Table14[[#This Row],[Grade Level]]</f>
         <v>2026</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="19.5">
+    <row r="43" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
         <v>5</v>
       </c>
@@ -16636,7 +16696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.5">
+    <row r="44" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16709,7 +16769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.5">
+    <row r="45" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16782,7 +16842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.5">
+    <row r="46" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16855,7 +16915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="38.25">
+    <row r="47" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16928,7 +16988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.5">
+    <row r="48" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -17001,7 +17061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5">
+    <row r="49" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -17074,7 +17134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.5">
+    <row r="50" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -17147,7 +17207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.5">
+    <row r="51" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -17220,7 +17280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.5">
+    <row r="52" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -17293,7 +17353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.5">
+    <row r="53" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17366,8 +17426,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" s="7" customFormat="1"/>
-    <row r="55" spans="1:27" ht="19.5">
+    <row r="54" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="55" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -17440,7 +17500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.5">
+    <row r="56" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17513,7 +17573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.5">
+    <row r="57" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17586,7 +17646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.5">
+    <row r="58" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17659,7 +17719,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="38.25">
+    <row r="59" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17732,7 +17792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.5">
+    <row r="60" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17805,7 +17865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.5">
+    <row r="61" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A61" s="37">
         <v>6</v>
       </c>
@@ -17878,7 +17938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.5">
+    <row r="62" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -17951,7 +18011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.5">
+    <row r="63" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -18024,7 +18084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.5">
+    <row r="64" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A64" s="37">
         <v>6</v>
       </c>
@@ -18097,7 +18157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.5">
+    <row r="65" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A65" s="1">
         <v>6</v>
       </c>
@@ -18170,8 +18230,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" s="7" customFormat="1"/>
-    <row r="67" spans="1:27" ht="19.5">
+    <row r="66" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="67" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>7</v>
       </c>
@@ -18240,7 +18300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.5">
+    <row r="68" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18309,7 +18369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.5">
+    <row r="69" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18378,7 +18438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.5">
+    <row r="70" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18447,7 +18507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="38.25">
+    <row r="71" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18516,7 +18576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.5">
+    <row r="72" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18585,7 +18645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.5">
+    <row r="73" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18654,7 +18714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.5">
+    <row r="74" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18723,7 +18783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.5">
+    <row r="75" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18792,7 +18852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.5">
+    <row r="76" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18861,7 +18921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.5">
+    <row r="77" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18930,8 +18990,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:27" s="7" customFormat="1"/>
-    <row r="79" spans="1:27" ht="19.5">
+    <row r="78" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>8</v>
       </c>
@@ -19000,7 +19060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.5">
+    <row r="80" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -19069,7 +19129,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.5">
+    <row r="81" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -19138,7 +19198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.5">
+    <row r="82" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -19207,7 +19267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.5">
+    <row r="83" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -19276,7 +19336,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.5">
+    <row r="84" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19345,7 +19405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.5">
+    <row r="85" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19414,7 +19474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.5">
+    <row r="86" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19483,7 +19543,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.5">
+    <row r="87" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19552,7 +19612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.5">
+    <row r="88" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19621,7 +19681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.5">
+    <row r="89" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19690,8 +19750,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.5">
+    <row r="90" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="91" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -19760,7 +19820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:27" ht="19.5">
+    <row r="92" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>9</v>
       </c>
@@ -19829,7 +19889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:27" ht="19.5">
+    <row r="93" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>9</v>
       </c>
@@ -19898,7 +19958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:27" ht="19.5">
+    <row r="94" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>9</v>
       </c>
@@ -19967,7 +20027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:27" ht="19.5">
+    <row r="95" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>9</v>
       </c>
@@ -20036,7 +20096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:27" ht="19.5">
+    <row r="96" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>9</v>
       </c>
@@ -20105,7 +20165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:27" ht="19.5">
+    <row r="97" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A97" s="38">
         <v>9</v>
       </c>
@@ -20174,7 +20234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:27" ht="19.5">
+    <row r="98" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>9</v>
       </c>
@@ -20243,7 +20303,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:27" ht="19.5">
+    <row r="99" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>9</v>
       </c>
@@ -20312,7 +20372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:27" ht="19.5">
+    <row r="100" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A100" s="38">
         <v>9</v>
       </c>
@@ -20381,7 +20441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:27" ht="19.5">
+    <row r="101" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>9</v>
       </c>
@@ -20450,8 +20510,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:27" s="7" customFormat="1"/>
-    <row r="103" spans="1:27" ht="19.5">
+    <row r="102" spans="1:27" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="103" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A103" s="10">
         <v>10</v>
       </c>
@@ -20520,7 +20580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:27" ht="19.5">
+    <row r="104" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A104" s="10">
         <v>10</v>
       </c>
@@ -20589,7 +20649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:27" ht="19.5">
+    <row r="105" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A105" s="10">
         <v>10</v>
       </c>
@@ -20658,7 +20718,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:27" ht="19.5">
+    <row r="106" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A106" s="10">
         <v>10</v>
       </c>
@@ -20727,7 +20787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:27" ht="19.5">
+    <row r="107" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A107" s="10">
         <v>10</v>
       </c>
@@ -20796,7 +20856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:27" ht="19.5">
+    <row r="108" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A108" s="10">
         <v>10</v>
       </c>
@@ -20865,7 +20925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:27" ht="19.5">
+    <row r="109" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A109" s="38">
         <v>10</v>
       </c>
@@ -20934,7 +20994,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:27" ht="19.5">
+    <row r="110" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A110" s="10">
         <v>10</v>
       </c>
@@ -21003,7 +21063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:27" ht="19.5">
+    <row r="111" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A111" s="10">
         <v>10</v>
       </c>
@@ -21072,7 +21132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:27" ht="19.5">
+    <row r="112" spans="1:27" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A112" s="38">
         <v>10</v>
       </c>
@@ -21141,7 +21201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="19.5">
+    <row r="113" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A113" s="10">
         <v>10</v>
       </c>
@@ -21210,13 +21270,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:28" s="7" customFormat="1">
+    <row r="114" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="F114" s="7">
         <f>2026 - Table14[[#This Row],[Grade Level]]</f>
         <v>2026</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="38.25">
+    <row r="115" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>26</v>
       </c>
@@ -21285,7 +21345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="19.5">
+    <row r="116" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>26</v>
       </c>
@@ -21354,7 +21414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="19.5">
+    <row r="117" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>26</v>
       </c>
@@ -21423,7 +21483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="19.5">
+    <row r="118" spans="1:28" ht="20.25" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>26</v>
       </c>
@@ -21492,7 +21552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:28" ht="38.25">
+    <row r="119" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>26</v>
       </c>
@@ -21561,7 +21621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:28" ht="38.25">
+    <row r="120" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>26</v>
       </c>
@@ -21630,7 +21690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="57.75">
+    <row r="121" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>26</v>
       </c>
@@ -21699,7 +21759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.25">
+    <row r="122" spans="1:28" ht="34.5" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>26</v>
       </c>
@@ -21768,8 +21828,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:28" s="7" customFormat="1"/>
-    <row r="124" spans="1:28">
+    <row r="123" spans="1:28" s="7" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="124" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A124" s="7"/>
       <c r="B124" s="7"/>
       <c r="C124" s="7"/>
@@ -21799,7 +21859,7 @@
       <c r="AA124" s="7"/>
       <c r="AB124" s="7"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A125" s="7"/>
       <c r="B125" s="7"/>
       <c r="C125" s="7"/>
@@ -21829,7 +21889,7 @@
       <c r="AA125" s="7"/>
       <c r="AB125" s="7"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A126" s="7"/>
       <c r="B126" s="7"/>
       <c r="C126" s="7"/>
@@ -21859,7 +21919,7 @@
       <c r="AA126" s="7"/>
       <c r="AB126" s="7"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A127" s="7"/>
       <c r="B127" s="7"/>
       <c r="C127" s="7"/>
@@ -21889,7 +21949,7 @@
       <c r="AA127" s="7"/>
       <c r="AB127" s="7"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A128" s="7"/>
       <c r="B128" s="7"/>
       <c r="C128" s="7"/>
@@ -21919,7 +21979,7 @@
       <c r="AA128" s="7"/>
       <c r="AB128" s="7"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A129" s="7"/>
       <c r="B129" s="7"/>
       <c r="C129" s="7"/>
@@ -21949,7 +22009,7 @@
       <c r="AA129" s="7"/>
       <c r="AB129" s="7"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A130" s="7"/>
       <c r="B130" s="7"/>
       <c r="C130" s="7"/>
@@ -21979,7 +22039,7 @@
       <c r="AA130" s="7"/>
       <c r="AB130" s="7"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A131" s="7"/>
       <c r="B131" s="7"/>
       <c r="C131" s="7"/>
@@ -22009,7 +22069,7 @@
       <c r="AA131" s="7"/>
       <c r="AB131" s="7"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A132" s="7"/>
       <c r="B132" s="7"/>
       <c r="C132" s="7"/>
@@ -22039,7 +22099,7 @@
       <c r="AA132" s="7"/>
       <c r="AB132" s="7"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A133" s="7"/>
       <c r="B133" s="7"/>
       <c r="C133" s="7"/>
@@ -22069,7 +22129,7 @@
       <c r="AA133" s="7"/>
       <c r="AB133" s="7"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A134" s="7"/>
       <c r="B134" s="7"/>
       <c r="C134" s="7"/>
@@ -22099,7 +22159,7 @@
       <c r="AA134" s="7"/>
       <c r="AB134" s="7"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A135" s="7"/>
       <c r="B135" s="7"/>
       <c r="C135" s="7"/>
@@ -22129,7 +22189,7 @@
       <c r="AA135" s="7"/>
       <c r="AB135" s="7"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A136" s="7"/>
       <c r="B136" s="7"/>
       <c r="C136" s="7"/>
@@ -22159,7 +22219,7 @@
       <c r="AA136" s="7"/>
       <c r="AB136" s="7"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A137" s="7"/>
       <c r="B137" s="7"/>
       <c r="C137" s="7"/>
@@ -22189,7 +22249,7 @@
       <c r="AA137" s="7"/>
       <c r="AB137" s="7"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A138" s="7"/>
       <c r="B138" s="7"/>
       <c r="C138" s="7"/>
@@ -22219,7 +22279,7 @@
       <c r="AA138" s="7"/>
       <c r="AB138" s="7"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A139" s="7"/>
       <c r="B139" s="7"/>
       <c r="C139" s="7"/>
@@ -22249,7 +22309,7 @@
       <c r="AA139" s="7"/>
       <c r="AB139" s="7"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A140" s="7"/>
       <c r="B140" s="7"/>
       <c r="C140" s="7"/>
